--- a/cases/liugong/04_投资明细.xlsx
+++ b/cases/liugong/04_投资明细.xlsx
@@ -34,15 +34,15 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">柳工配件库智能化升级 </t>
+      <t xml:space="preserve">仓库自动化升级 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="16"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -72,8 +72,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -91,8 +91,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">±20%</t>
@@ -126,8 +126,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(</t>
@@ -147,8 +147,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
@@ -374,8 +374,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ASRS</t>
@@ -393,8 +393,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">2,500–3,500 </t>
@@ -412,8 +412,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -431,8 +431,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">30% · </t>
@@ -450,8 +450,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&gt;6</t>
@@ -469,8 +469,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Shuttle </t>
@@ -488,8 +488,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">800–1,200 </t>
@@ -507,8 +507,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -526,8 +526,8 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">35%</t>
@@ -558,8 +558,8 @@
         <b val="true"/>
         <sz val="15"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/ </t>
@@ -579,8 +579,8 @@
         <b val="true"/>
         <sz val="15"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/ </t>
@@ -618,8 +618,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(</t>
@@ -639,8 +639,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
@@ -665,8 +665,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(</t>
@@ -686,8 +686,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
@@ -712,8 +712,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· 100% </t>
@@ -854,8 +854,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">GPS </t>
@@ -930,8 +930,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+ MES </t>
@@ -961,8 +961,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1/2/3 </t>
@@ -980,8 +980,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">MES </t>
@@ -1015,8 +1015,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -1543,8 +1543,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/</t>
@@ -1564,8 +1564,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/</t>
@@ -1640,8 +1640,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -1676,8 +1676,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">WiFi </t>
@@ -1707,8 +1707,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -1726,8 +1726,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">AP </t>
@@ -1758,8 +1758,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/ </t>
@@ -1789,8 +1789,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">AGV </t>
@@ -1808,8 +1808,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+ </t>
@@ -1853,8 +1853,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">300 lux</t>
@@ -1882,8 +1882,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+</t>
@@ -1916,8 +1916,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">±20%</t>
@@ -1935,8 +1935,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">=</t>
@@ -1954,8 +1954,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">3-5 </t>
@@ -1973,8 +1973,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">100% </t>
@@ -1992,8 +1992,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">v0.4 </t>
@@ -2011,8 +2011,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">50%</t>
@@ -2043,8 +2043,8 @@
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -2064,8 +2064,8 @@
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
@@ -2097,8 +2097,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/</t>
@@ -2190,8 +2190,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+ AI </t>
@@ -2209,8 +2209,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/</t>
@@ -2228,8 +2228,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/</t>
@@ -2247,8 +2247,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">WMS </t>
@@ -2298,7 +2298,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="DejaVu Sans"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2345,14 +2345,14 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">发货前最后一关整车扫描，与柳工 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+      <t xml:space="preserve">发货前最后一关整车扫描，与客户 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">MES </t>
@@ -2402,7 +2402,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="DejaVu Sans"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2514,8 +2514,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0mm </t>
@@ -2533,8 +2533,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">AGV/</t>
@@ -2584,7 +2584,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="DejaVu Sans"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2617,8 +2617,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFC13C2E"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">202 </t>
@@ -2636,8 +2636,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFC13C2E"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">170 </t>
@@ -2655,8 +2655,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFC13C2E"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">±20%</t>
@@ -2699,8 +2699,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(</t>
@@ -2720,8 +2720,8 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
@@ -2743,8 +2743,8 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+ </t>
@@ -2770,6 +2770,581 @@
       </rPr>
       <t xml:space="preserve">第 </t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1–6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WMS/TMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上线、货位编码细化、工位器具标准化、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDA+RFID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">试点、流程重构、工业 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">② 核心区自动化设备</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7–18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区货架</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+AGV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">货到人 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AMR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">批次锁定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">视觉、集货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复核</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+RFID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">龙门、登车桥、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">调度初上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 长尾覆盖 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通用化复制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19–30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mezzanine+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">货架、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区悬臂货架、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">决策闭环、经验沉淀模板、向其他节点平移</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">合计</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7A6A4F"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">注：三期合计 ≈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7A6A4F"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,165 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7A6A4F"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万，与投资明细总额一致；每期均可独立见效并为下期铺路。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASRS / Shuttle / </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">五区混合 选型对比</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">方案</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投资估算</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万元</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">回收期</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结论</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">① 全 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASRS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">覆盖</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2,500–3,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤30%</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2778,7 +3353,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1–6 </t>
+      <t xml:space="preserve">&gt; 6 </t>
     </r>
     <r>
       <rPr>
@@ -2787,81 +3362,82 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">个月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WMS/TMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上线、货位编码细化、工位器具标准化、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDA+RFID </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">试点、流程重构、工业 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WiFi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部署</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">② 核心区自动化设备</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第 </t>
-    </r>
+      <t xml:space="preserve">年</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">极差</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✗ SKU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">异质</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长尾拆零，与高密度单元化不符</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">② Shuttle </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2B4A"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">驶入式</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">800–1,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤35%</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2870,7 +3446,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7–18 </t>
+      <t xml:space="preserve">&gt; 5 </t>
     </r>
     <r>
       <rPr>
@@ -2879,225 +3455,52 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">个月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区货架</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+AGV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">货到人 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AMR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">批次锁定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">视觉、集货</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">复核</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+RFID </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">龙门、登车桥、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">调度初上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 长尾覆盖 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通用化复制</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第 </t>
-    </r>
+      <t xml:space="preserve">年</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">差</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">✗ 适合少品类大批量，与多品类小批量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JIT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相反</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 五区混合（推荐）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈ 1,165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈50%</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3106,7 +3509,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">19–30 </t>
+      <t xml:space="preserve">≈ 3 </t>
     </r>
     <r>
       <rPr>
@@ -3115,413 +3518,10 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">个月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mezzanine+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">货架、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区悬臂货架、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">决策闭环、经验沉淀模板、向其他节点平移</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">合计</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7A6A4F"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">注：三期合计 ≈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7A6A4F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,165 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7A6A4F"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万，与投资明细总额一致；每期均可独立见效并为下期铺路。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASRS / Shuttle / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">五区混合 选型对比</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">方案</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投资估算</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万元</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">回收期</t>
-  </si>
-  <si>
-    <t xml:space="preserve">结论</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 全 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASRS </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">覆盖</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2,500–3,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤30%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; 6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">年</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">极差</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">✗ SKU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">异质</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长尾拆零，与高密度单元化不符</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">② Shuttle </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A2B4A"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">驶入式</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">800–1,200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤35%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; 5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">差</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">✗ 适合少品类大批量，与多品类小批量 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JIT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相反</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">③ 五区混合（推荐）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≈ 1,165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≈50%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">≈ 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">强</t>
   </si>
   <si>
@@ -3538,8 +3538,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">SKU </t>
@@ -3557,8 +3557,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">+</t>
@@ -3584,7 +3584,7 @@
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3618,8 +3618,8 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF1A2B4A"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3631,8 +3631,8 @@
     <font>
       <sz val="9"/>
       <color rgb="FF7A6A4F"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3646,8 +3646,8 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3693,8 +3693,8 @@
     <font>
       <sz val="10"/>
       <color rgb="FF7A6A4F"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3708,8 +3708,16 @@
       <b val="true"/>
       <sz val="15"/>
       <color rgb="FF1A2B4A"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1A2B4A"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3747,6 +3755,21 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1A2B4A"/>
@@ -3757,8 +3780,8 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1A2B4A"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3778,8 +3801,15 @@
       <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1A2B4A"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3791,6 +3821,14 @@
     <font>
       <sz val="9"/>
       <color rgb="FFC13C2E"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1A2B4A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -3807,6 +3845,21 @@
       <color rgb="FF000000"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1A2B4A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3884,16 +3937,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3933,11 +3990,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3945,19 +4002,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3969,11 +4026,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3981,7 +4038,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4009,7 +4066,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4017,7 +4074,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4025,19 +4082,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4045,31 +4102,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4328,151 +4385,151 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <f aca="false">投资明细!D9</f>
         <v>300</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <f aca="false">B5/$B$8</f>
         <v>0.257510729613734</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <f aca="false">投资明细!D17</f>
         <v>810</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">B6/$B$8</f>
         <v>0.695278969957082</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <f aca="false">投资明细!D23</f>
         <v>55</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <f aca="false">B7/$B$8</f>
         <v>0.0472103004291846</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="10" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>1165</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <f aca="false">B8/$B$8</f>
         <v>1</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <f aca="false">B5/$B$8</f>
         <v>0.257510729613734</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <f aca="false">B6/$B$8</f>
         <v>0.695278969957082</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <f aca="false">B7/$B$8</f>
         <v>0.0472103004291846</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4498,541 +4555,541 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <f aca="false">D5*E5</f>
         <v>120</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <f aca="false">D6*E6</f>
         <v>40</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <f aca="false">D7*E7</f>
         <v>80</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <f aca="false">D8*E8</f>
         <v>60</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="25" t="n">
+      <c r="C9" s="24"/>
+      <c r="D9" s="26" t="n">
         <f aca="false">SUM(D5:D8)</f>
         <v>300</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">F9/D9</f>
         <v>1</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="28" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>300</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <f aca="false">D11*E11</f>
         <v>105</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>0.65</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <f aca="false">D12*E12</f>
         <v>110.5</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>230</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>0.55</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <f aca="false">D13*E13</f>
         <v>126.5</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <f aca="false">D14*E14</f>
         <v>30</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <f aca="false">D15*E15</f>
         <v>7.5</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>0.55</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="20" t="n">
         <f aca="false">D16*E16</f>
         <v>93.5</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="25" t="n">
+      <c r="C17" s="24"/>
+      <c r="D17" s="26" t="n">
         <f aca="false">SUM(D11:D16)</f>
         <v>810</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <f aca="false">F17/D17</f>
         <v>0.583950617283951</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="28" t="n">
         <f aca="false">SUM(F11:F16)</f>
         <v>473</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="20" t="n">
         <f aca="false">D19*E19</f>
         <v>6.6</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="20" t="n">
         <f aca="false">D20*E20</f>
         <v>1.8</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="20" t="n">
         <f aca="false">D21*E21</f>
         <v>0</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="20" t="n">
         <f aca="false">D22*E22</f>
         <v>1</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="25" t="n">
+      <c r="C23" s="24"/>
+      <c r="D23" s="26" t="n">
         <f aca="false">SUM(D19:D22)</f>
         <v>55</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="27" t="n">
         <f aca="false">F23/D23</f>
         <v>0.170909090909091</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="28" t="n">
         <f aca="false">SUM(F19:F22)</f>
         <v>9.4</v>
       </c>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28"/>
-      <c r="B25" s="8" t="s">
+      <c r="G23" s="24"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29"/>
+      <c r="B25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29" t="n">
+      <c r="C25" s="29"/>
+      <c r="D25" s="30" t="n">
         <f aca="false">D9+D17+D23</f>
         <v>1165</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="30" t="n">
+      <c r="E25" s="29"/>
+      <c r="F25" s="31" t="n">
         <f aca="false">F9+F17+F23</f>
         <v>782.4</v>
       </c>
-      <c r="G25" s="28"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="31" t="s">
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="32" t="n">
+      <c r="E26" s="33" t="n">
         <f aca="false">(F17+F23)/(D17+D23)</f>
         <v>0.557687861271676</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="33" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="32" t="n">
+      <c r="E27" s="33" t="n">
         <f aca="false">(F9+F17+F23)/D25</f>
         <v>0.671587982832618</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="35"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="35"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5060,150 +5117,150 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="25" t="n">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="26" t="n">
         <f aca="false">SUM(D4:D8)</f>
         <v>202</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5228,100 +5285,100 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-    </row>
-    <row r="3" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+    </row>
+    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>320</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>750</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29" t="n">
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30" t="n">
         <f aca="false">SUM(D4:D6)</f>
         <v>1165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5346,100 +5403,100 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="42" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="44" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="47" t="s">
         <v>134</v>
       </c>
     </row>
